--- a/consent_forms/046_visage_covid_19_liability_release_waiver--consent_forms.xlsx
+++ b/consent_forms/046_visage_covid_19_liability_release_waiver--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'fever',_'value':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Fever', 'value': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cough',_'value':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cough', 'value': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue',_'value':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue', 'value': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'headache',_'value':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Headache', 'value': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'asthma',_'value':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Asthma', 'value': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'heart_disease',_'value':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Disease', 'value': 'Heart Disease'}</t>
+          <t>Heart Disease</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
